--- a/backend/outputs/output_basicat/LOG/prod/applications_ip.xlsx
+++ b/backend/outputs/output_basicat/LOG/prod/applications_ip.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -625,74 +625,6 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>oplogis149</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>10.20.1.159</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>10009</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>oplogis167</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>10.20.1.177</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>10009</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>oplogis179</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>10.20.1.189</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>10009</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>oplogis191</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>10.20.1.201</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>10009</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
